--- a/java/dubbo/dubbo_code.xlsx
+++ b/java/dubbo/dubbo_code.xlsx
@@ -4,36 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" activeTab="5"/>
+    <workbookView windowWidth="22368" windowHeight="9564" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet19" sheetId="21" r:id="rId1"/>
-    <sheet name="Sheet20" sheetId="22" r:id="rId2"/>
-    <sheet name="Sheet21" sheetId="23" r:id="rId3"/>
-    <sheet name="Sheet22" sheetId="24" r:id="rId4"/>
-    <sheet name="Sheet23" sheetId="25" r:id="rId5"/>
-    <sheet name="Sheet24" sheetId="26" r:id="rId6"/>
+    <sheet name="Sheet10" sheetId="36" r:id="rId1"/>
+    <sheet name="Sheet11" sheetId="37" r:id="rId2"/>
+    <sheet name="Sheet12" sheetId="38" r:id="rId3"/>
+    <sheet name="Sheet13" sheetId="39" r:id="rId4"/>
+    <sheet name="Sheet14" sheetId="40" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <r>
       <rPr>
-        <i/>
         <sz val="12"/>
-        <color rgb="FF871094"/>
+        <color rgb="FF080808"/>
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>org.apache.dubbo.rpc.protocol.rest</t>
+      <t>org.apache.dubbo.remoting.transport</t>
     </r>
-  </si>
-  <si>
-    <t>org.apache.dubbo.rpc.protocol.rest</t>
   </si>
   <si>
     <r>
@@ -48,10 +43,7 @@
     </r>
   </si>
   <si>
-    <t>Constants</t>
-  </si>
-  <si>
-    <t>RestProtocolServer</t>
+    <t>ChannelHandlerDelegate</t>
   </si>
   <si>
     <r>
@@ -66,115 +58,49 @@
     </r>
   </si>
   <si>
-    <t>BaseRestProtocolServer</t>
-  </si>
-  <si>
-    <t>DubboHttpProtocolServer</t>
-  </si>
-  <si>
-    <t>DubboResourceFactory</t>
-  </si>
-  <si>
-    <t>NettyRestProtocolServer</t>
-  </si>
-  <si>
-    <t>RestConstraintViolation</t>
-  </si>
-  <si>
-    <t>RestProtocol</t>
-  </si>
-  <si>
-    <t>RestServerFactory</t>
-  </si>
-  <si>
-    <t>RpcContextFilter</t>
-  </si>
-  <si>
-    <t>RpcExceptionMapper</t>
-  </si>
-  <si>
-    <t>ViolationReport</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF871094"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
-      <t>org.apache.dubbo.rpc.protocol.thrift</t>
-    </r>
-  </si>
-  <si>
-    <t>ClassNameGenerator</t>
-  </si>
-  <si>
-    <t>DubboClassNameGenerator</t>
-  </si>
-  <si>
-    <t>ThriftClassNameGenerator</t>
-  </si>
-  <si>
-    <t>ThriftCodec</t>
-  </si>
-  <si>
-    <t>ThriftConstants</t>
-  </si>
-  <si>
-    <t>ThriftInvoker</t>
-  </si>
-  <si>
-    <t>ThriftNativeCodec</t>
-  </si>
-  <si>
-    <t>ThriftProtocol</t>
-  </si>
-  <si>
-    <t>ThriftUtils</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9.75"/>
-        <color rgb="FF353833"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>枚举</t>
-    </r>
-  </si>
-  <si>
-    <t>ThriftType</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF871094"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
-      <t>org.apache.dubbo.rpc.service</t>
-    </r>
-  </si>
-  <si>
-    <t>Destroyable</t>
-  </si>
-  <si>
-    <t>EchoService</t>
-  </si>
-  <si>
-    <t>GenericService</t>
-  </si>
-  <si>
-    <t>EchoServiceDetector</t>
-  </si>
-  <si>
-    <t>GenericServiceDetector</t>
+    <t>AbstractChannel</t>
+  </si>
+  <si>
+    <t>AbstractChannelHandlerDelegate</t>
+  </si>
+  <si>
+    <t>AbstractClient</t>
+  </si>
+  <si>
+    <t>AbstractCodec</t>
+  </si>
+  <si>
+    <t>AbstractEndpoint</t>
+  </si>
+  <si>
+    <t>AbstractPeer</t>
+  </si>
+  <si>
+    <t>AbstractServer</t>
+  </si>
+  <si>
+    <t>ChannelDelegate</t>
+  </si>
+  <si>
+    <t>ChannelHandlerAdapter</t>
+  </si>
+  <si>
+    <t>ChannelHandlerDispatcher</t>
+  </si>
+  <si>
+    <t>ClientDelegate</t>
+  </si>
+  <si>
+    <t>CodecSupport</t>
+  </si>
+  <si>
+    <t>DecodeHandler</t>
+  </si>
+  <si>
+    <t>MultiMessageHandler</t>
+  </si>
+  <si>
+    <t>ServerDelegate</t>
   </si>
   <si>
     <r>
@@ -189,7 +115,33 @@
     </r>
   </si>
   <si>
-    <t>GenericException</t>
+    <t>ExceedPayloadLimitException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF080808"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.apache.dubbo.remoting.transport.grizzly</t>
+    </r>
+  </si>
+  <si>
+    <t>GrizzlyClient</t>
+  </si>
+  <si>
+    <t>GrizzlyCodecAdapter</t>
+  </si>
+  <si>
+    <t>GrizzlyHandler</t>
+  </si>
+  <si>
+    <t>GrizzlyServer</t>
+  </si>
+  <si>
+    <t>GrizzlyTransporter</t>
   </si>
   <si>
     <r>
@@ -200,26 +152,20 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>org.apache.dubbo.rpc.support</t>
+      <t>org.apache.dubbo.remoting.transport.mina</t>
     </r>
   </si>
   <si>
-    <t>AccessLogData</t>
-  </si>
-  <si>
-    <t>GroupServiceKeyCache</t>
-  </si>
-  <si>
-    <t>MockInvoker</t>
-  </si>
-  <si>
-    <t>MockProtocol</t>
-  </si>
-  <si>
-    <t>ProtocolUtils</t>
-  </si>
-  <si>
-    <t>RpcUtils</t>
+    <t>MinaClient</t>
+  </si>
+  <si>
+    <t>MinaHandler</t>
+  </si>
+  <si>
+    <t>MinaServer</t>
+  </si>
+  <si>
+    <t>MinaTransporter</t>
   </si>
   <si>
     <r>
@@ -230,23 +176,26 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>org.apache.dubbo.serialize.hessian</t>
+      <t>org.apache.dubbo.remoting.transport.netty</t>
     </r>
   </si>
   <si>
-    <t>Hessian2ObjectInput</t>
-  </si>
-  <si>
-    <t>Hessian2ObjectOutput</t>
-  </si>
-  <si>
-    <t>Hessian2Serialization</t>
-  </si>
-  <si>
-    <t>Hessian2SerializerFactory</t>
-  </si>
-  <si>
-    <t>Java8SerializerFactory</t>
+    <t>NettyBackedChannelBuffer</t>
+  </si>
+  <si>
+    <t>NettyBackedChannelBufferFactory</t>
+  </si>
+  <si>
+    <t>NettyClient</t>
+  </si>
+  <si>
+    <t>NettyHandler</t>
+  </si>
+  <si>
+    <t>NettyServer</t>
+  </si>
+  <si>
+    <t>NettyTransporter</t>
   </si>
   <si>
     <r>
@@ -257,56 +206,35 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>org.apache.dubbo.serialize.hessian.serializer.java8</t>
+      <t>org.apache.dubbo.remoting.transport.netty4</t>
     </r>
   </si>
   <si>
-    <t>DurationHandle</t>
-  </si>
-  <si>
-    <t>InstantHandle</t>
-  </si>
-  <si>
-    <t>Java8TimeSerializer</t>
-  </si>
-  <si>
-    <t>LocalDateHandle</t>
-  </si>
-  <si>
-    <t>LocalDateTimeHandle</t>
-  </si>
-  <si>
-    <t>LocalTimeHandle</t>
-  </si>
-  <si>
-    <t>MonthDayHandle</t>
-  </si>
-  <si>
-    <t>OffsetDateTimeHandle</t>
-  </si>
-  <si>
-    <t>OffsetTimeHandle</t>
-  </si>
-  <si>
-    <t>PeriodHandle</t>
-  </si>
-  <si>
-    <t>YearHandle</t>
-  </si>
-  <si>
-    <t>YearMonthHandle</t>
-  </si>
-  <si>
-    <t>ZonedDateTimeHandle</t>
-  </si>
-  <si>
-    <t>ZoneIdHandle</t>
-  </si>
-  <si>
-    <t>ZoneIdSerializer</t>
-  </si>
-  <si>
-    <t>ZoneOffsetHandle</t>
+    <t>NettyClientHandler</t>
+  </si>
+  <si>
+    <t>NettyCodecAdapter</t>
+  </si>
+  <si>
+    <t>NettyEventLoopFactory</t>
+  </si>
+  <si>
+    <t>NettyServerHandler</t>
+  </si>
+  <si>
+    <t>SslContexts</t>
+  </si>
+  <si>
+    <t>SslHandlerInitializer</t>
+  </si>
+  <si>
+    <t>SslHandlerInitializer.HandshakeCompletionEvent</t>
+  </si>
+  <si>
+    <t>SslHandlerInitializer.SslClientTlsHandler</t>
+  </si>
+  <si>
+    <t>SslHandlerInitializer.SslServerTlsHandler</t>
   </si>
 </sst>
 </file>
@@ -319,7 +247,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +266,31 @@
       <b/>
       <sz val="9.75"/>
       <color rgb="FF353833"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF4A6782"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFBB7A2A"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF080808"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF4A6782"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -794,10 +747,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -806,145 +759,157 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1265,90 +1230,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="93.6" spans="1:1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="4" ht="45.6" spans="1:1">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="8" ht="22.8" spans="1:1">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
+    <row r="9" ht="57" spans="1:1">
+      <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+    <row r="10" ht="22.8" spans="1:1">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+    <row r="11" ht="22.8" spans="1:1">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+    <row r="12" ht="34.2" spans="1:1">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+    <row r="13" ht="22.8" spans="1:1">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="14" ht="22.8" spans="1:1">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+    <row r="15" ht="34.2" spans="1:1">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="16" ht="34.2" spans="1:1">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+    <row r="17" ht="45.6" spans="1:1">
+      <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="18" ht="22.8" spans="1:1">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+    <row r="19" ht="22.8" spans="1:1">
+      <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="20" ht="22.8" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="34.2" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" ht="22.8" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" ht="45.6" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="ChannelHandlerDelegate" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ChannelHandlerDelegate.html"/>
+    <hyperlink ref="A8" r:id="rId2" display="AbstractChannel" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractChannel.html"/>
+    <hyperlink ref="A9" r:id="rId3" display="AbstractChannelHandlerDelegate" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractChannelHandlerDelegate.html"/>
+    <hyperlink ref="A10" r:id="rId4" display="AbstractClient" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractClient.html"/>
+    <hyperlink ref="A11" r:id="rId5" display="AbstractCodec" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractCodec.html"/>
+    <hyperlink ref="A12" r:id="rId6" display="AbstractEndpoint" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractEndpoint.html"/>
+    <hyperlink ref="A13" r:id="rId7" display="AbstractPeer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractPeer.html"/>
+    <hyperlink ref="A14" r:id="rId8" display="AbstractServer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/AbstractServer.html"/>
+    <hyperlink ref="A15" r:id="rId9" display="ChannelDelegate" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ChannelDelegate.html"/>
+    <hyperlink ref="A16" r:id="rId10" display="ChannelHandlerAdapter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ChannelHandlerAdapter.html"/>
+    <hyperlink ref="A17" r:id="rId11" display="ChannelHandlerDispatcher" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ChannelHandlerDispatcher.html"/>
+    <hyperlink ref="A18" r:id="rId12" display="ClientDelegate" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ClientDelegate.html"/>
+    <hyperlink ref="A19" r:id="rId13" display="CodecSupport" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/CodecSupport.html"/>
+    <hyperlink ref="A20" r:id="rId14" display="DecodeHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/DecodeHandler.html"/>
+    <hyperlink ref="A21" r:id="rId15" display="MultiMessageHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/MultiMessageHandler.html"/>
+    <hyperlink ref="A22" r:id="rId16" display="ServerDelegate" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ServerDelegate.html"/>
+    <hyperlink ref="A26" r:id="rId17" display="ExceedPayloadLimitException" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/ExceedPayloadLimitException.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1357,80 +1366,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+    <row r="1" ht="124.8" spans="1:1">
+      <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="22.8" spans="1:1">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+    <row r="5" ht="34.2" spans="1:1">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+    <row r="6" ht="22.8" spans="1:1">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="7" ht="22.8" spans="1:1">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
+    <row r="8" ht="34.2" spans="1:1">
+      <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="GrizzlyClient" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/grizzly/GrizzlyClient.html"/>
+    <hyperlink ref="A5" r:id="rId2" display="GrizzlyCodecAdapter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/grizzly/GrizzlyCodecAdapter.html"/>
+    <hyperlink ref="A6" r:id="rId3" display="GrizzlyHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/grizzly/GrizzlyHandler.html"/>
+    <hyperlink ref="A7" r:id="rId4" display="GrizzlyServer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/grizzly/GrizzlyServer.html"/>
+    <hyperlink ref="A8" r:id="rId5" display="GrizzlyTransporter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/grizzly/GrizzlyTransporter.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1439,60 +1420,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
+    <row r="1" ht="109.2" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="22.8" spans="1:1">
+      <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="5" ht="22.8" spans="1:1">
+      <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="6" ht="22.8" spans="1:1">
+      <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="7" ht="22.8" spans="1:1">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="MinaClient" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/mina/MinaClient.html"/>
+    <hyperlink ref="A5" r:id="rId2" display="MinaHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/mina/MinaHandler.html"/>
+    <hyperlink ref="A6" r:id="rId3" display="MinaServer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/mina/MinaServer.html"/>
+    <hyperlink ref="A7" r:id="rId4" display="MinaTransporter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/mina/MinaTransporter.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1501,50 +1468,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
+    <row r="1" ht="109.2" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="45.6" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="57" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="22.8" spans="1:1">
+      <c r="A6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="22.8" spans="1:1">
+      <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="8" ht="22.8" spans="1:1">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="9" ht="22.8" spans="1:1">
+      <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="NettyBackedChannelBuffer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty/NettyBackedChannelBuffer.html"/>
+    <hyperlink ref="A5" r:id="rId2" display="NettyBackedChannelBufferFactory" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty/NettyBackedChannelBufferFactory.html"/>
+    <hyperlink ref="A6" r:id="rId3" display="NettyClient" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty/NettyClient.html"/>
+    <hyperlink ref="A7" r:id="rId4" display="NettyHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty/NettyHandler.html"/>
+    <hyperlink ref="A8" r:id="rId5" display="NettyServer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty/NettyServer.html"/>
+    <hyperlink ref="A9" r:id="rId6" display="NettyTransporter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty/NettyTransporter.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1553,147 +1528,100 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
+    <row r="1" ht="124.8" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="45.6" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="22.8" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="34.2" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" ht="34.2" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="34.2" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" ht="22.8" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="34.2" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" ht="22.8" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="22.8" spans="1:1">
+      <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="13" ht="34.2" spans="1:1">
+      <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="14" ht="79.8" spans="1:1">
+      <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="15" ht="68.4" spans="1:1">
+      <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="16" ht="68.4" spans="1:1">
+      <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="NettyBackedChannelBuffer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyBackedChannelBuffer.html"/>
+    <hyperlink ref="A5" r:id="rId2" display="NettyClient" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyClient.html"/>
+    <hyperlink ref="A6" r:id="rId3" display="NettyClientHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyClientHandler.html"/>
+    <hyperlink ref="A7" r:id="rId4" display="NettyCodecAdapter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyCodecAdapter.html"/>
+    <hyperlink ref="A8" r:id="rId5" display="NettyEventLoopFactory" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyEventLoopFactory.html"/>
+    <hyperlink ref="A9" r:id="rId6" display="NettyServer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyServer.html"/>
+    <hyperlink ref="A10" r:id="rId7" display="NettyServerHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyServerHandler.html"/>
+    <hyperlink ref="A11" r:id="rId8" display="NettyTransporter" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/NettyTransporter.html"/>
+    <hyperlink ref="A12" r:id="rId9" display="SslContexts" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/SslContexts.html"/>
+    <hyperlink ref="A13" r:id="rId10" display="SslHandlerInitializer" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/SslHandlerInitializer.html"/>
+    <hyperlink ref="A14" r:id="rId11" display="SslHandlerInitializer.HandshakeCompletionEvent" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/SslHandlerInitializer.HandshakeCompletionEvent.html"/>
+    <hyperlink ref="A15" r:id="rId12" display="SslHandlerInitializer.SslClientTlsHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/SslHandlerInitializer.SslClientTlsHandler.html"/>
+    <hyperlink ref="A16" r:id="rId13" display="SslHandlerInitializer.SslServerTlsHandler" tooltip="https://javadoc.dev/online/api/org.apache.dubbo/dubbo/2.7.8/org/apache/dubbo/remoting/transport/netty4/SslHandlerInitializer.SslServerTlsHandler.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
